--- a/inst/extdata/MetricScoring.xlsx
+++ b/inst/extdata/MetricScoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BioMonTools_BenB/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="6_{E1038586-8D02-4FF7-859A-8FC7A176EA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BBE879A-1912-4C4D-B628-D05FDEF0E72C}"/>
+  <xr:revisionPtr revIDLastSave="442" documentId="6_{E1038586-8D02-4FF7-859A-8FC7A176EA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34441B10-4786-4982-8DCD-0D968C2F4D4C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$767</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$813</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ScoringRegimes!$A$5:$C$17</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
@@ -1671,7 +1671,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9958" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10065" uniqueCount="1049">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -4803,6 +4803,21 @@
   </si>
   <si>
     <t>17.81</t>
+  </si>
+  <si>
+    <t>WetWide_611489</t>
+  </si>
+  <si>
+    <t>100 * (18.43 - metric) / (18.43 - 0.23)</t>
+  </si>
+  <si>
+    <t>100 * (metric - 66.67) / (87.87 - 66.67)</t>
+  </si>
+  <si>
+    <t>Narrow_52949</t>
+  </si>
+  <si>
+    <t>100 * (6.03 - metric) / (6.03 - 3.31)</t>
   </si>
 </sst>
 </file>
@@ -5138,7 +5153,187 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="122">
+  <dxfs count="140">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -6371,7 +6566,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="121">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="139">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A18&amp;"!A1",A18)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7521,18 +7716,18 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:AP802"/>
+  <dimension ref="A1:AP813"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" customWidth="1"/>
-    <col min="9" max="9" width="38.5703125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
     <col min="10" max="10" width="40.42578125" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" customWidth="1"/>
     <col min="12" max="12" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -40193,485 +40388,892 @@
         <v>446</v>
       </c>
     </row>
+    <row r="803" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A803" t="s">
+        <v>998</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C803" t="s">
+        <v>74</v>
+      </c>
+      <c r="D803" t="s">
+        <v>28</v>
+      </c>
+      <c r="E803">
+        <v>0.23</v>
+      </c>
+      <c r="F803" t="s">
+        <v>78</v>
+      </c>
+      <c r="G803">
+        <v>18.43</v>
+      </c>
+      <c r="H803" t="s">
+        <v>80</v>
+      </c>
+      <c r="J803" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K803" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="804" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A804" t="s">
+        <v>998</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C804" t="s">
+        <v>85</v>
+      </c>
+      <c r="D804" t="s">
+        <v>28</v>
+      </c>
+      <c r="E804">
+        <v>0.91</v>
+      </c>
+      <c r="F804" t="s">
+        <v>78</v>
+      </c>
+      <c r="G804">
+        <v>30.01</v>
+      </c>
+      <c r="H804" t="s">
+        <v>80</v>
+      </c>
+      <c r="J804" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K804" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="805" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A805" t="s">
+        <v>998</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C805" t="s">
+        <v>34</v>
+      </c>
+      <c r="D805" t="s">
+        <v>28</v>
+      </c>
+      <c r="E805">
+        <v>3.89</v>
+      </c>
+      <c r="F805" t="s">
+        <v>78</v>
+      </c>
+      <c r="G805" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H805" t="s">
+        <v>80</v>
+      </c>
+      <c r="J805" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K805" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="806" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A806" t="s">
+        <v>998</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C806" t="s">
+        <v>133</v>
+      </c>
+      <c r="D806" t="s">
+        <v>14</v>
+      </c>
+      <c r="E806">
+        <v>3.56</v>
+      </c>
+      <c r="F806" t="s">
+        <v>78</v>
+      </c>
+      <c r="G806">
+        <v>31.95</v>
+      </c>
+      <c r="H806" t="s">
+        <v>80</v>
+      </c>
+      <c r="J806" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K806" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="807" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A807" t="s">
+        <v>998</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C807" t="s">
+        <v>683</v>
+      </c>
+      <c r="D807" t="s">
+        <v>14</v>
+      </c>
+      <c r="E807">
+        <v>66.67</v>
+      </c>
+      <c r="F807" t="s">
+        <v>78</v>
+      </c>
+      <c r="G807">
+        <v>87.87</v>
+      </c>
+      <c r="H807" t="s">
+        <v>80</v>
+      </c>
+      <c r="J807" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K807" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="808" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A808" t="s">
+        <v>998</v>
+      </c>
+      <c r="B808" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C808" t="s">
+        <v>87</v>
+      </c>
+      <c r="D808" t="s">
+        <v>14</v>
+      </c>
+      <c r="E808">
+        <v>3.02</v>
+      </c>
+      <c r="F808" t="s">
+        <v>78</v>
+      </c>
+      <c r="G808">
+        <v>35.81</v>
+      </c>
+      <c r="H808" t="s">
+        <v>80</v>
+      </c>
+      <c r="J808" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K808" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="809" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A809" t="s">
+        <v>998</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C809" t="s">
+        <v>135</v>
+      </c>
+      <c r="D809" t="s">
+        <v>28</v>
+      </c>
+      <c r="E809">
+        <v>3.31</v>
+      </c>
+      <c r="F809" t="s">
+        <v>78</v>
+      </c>
+      <c r="G809">
+        <v>6.03</v>
+      </c>
+      <c r="H809" t="s">
+        <v>80</v>
+      </c>
+      <c r="J809" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K809" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="810" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A810" t="s">
+        <v>998</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C810" t="s">
+        <v>430</v>
+      </c>
+      <c r="D810" t="s">
+        <v>28</v>
+      </c>
+      <c r="E810">
+        <v>2</v>
+      </c>
+      <c r="F810" t="s">
+        <v>78</v>
+      </c>
+      <c r="G810">
+        <v>10.35</v>
+      </c>
+      <c r="H810" t="s">
+        <v>80</v>
+      </c>
+      <c r="J810" t="s">
+        <v>1001</v>
+      </c>
+      <c r="K810" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="811" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A811" t="s">
+        <v>998</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C811" t="s">
+        <v>239</v>
+      </c>
+      <c r="D811" t="s">
+        <v>28</v>
+      </c>
+      <c r="E811">
+        <v>0.86</v>
+      </c>
+      <c r="F811" t="s">
+        <v>78</v>
+      </c>
+      <c r="G811">
+        <v>52.68</v>
+      </c>
+      <c r="H811" t="s">
+        <v>80</v>
+      </c>
+      <c r="J811" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K811" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="812" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A812" t="s">
+        <v>998</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C812" t="s">
+        <v>516</v>
+      </c>
+      <c r="D812" t="s">
+        <v>14</v>
+      </c>
+      <c r="E812">
+        <v>28.12</v>
+      </c>
+      <c r="F812" t="s">
+        <v>78</v>
+      </c>
+      <c r="G812">
+        <v>61.5</v>
+      </c>
+      <c r="H812" t="s">
+        <v>80</v>
+      </c>
+      <c r="J812" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K812" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="813" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A813" t="s">
+        <v>998</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C813" t="s">
+        <v>89</v>
+      </c>
+      <c r="D813" t="s">
+        <v>14</v>
+      </c>
+      <c r="E813">
+        <v>12.5</v>
+      </c>
+      <c r="F813" t="s">
+        <v>78</v>
+      </c>
+      <c r="G813">
+        <v>27.16</v>
+      </c>
+      <c r="H813" t="s">
+        <v>80</v>
+      </c>
+      <c r="J813" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K813" t="s">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP767" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
+  <autoFilter ref="A1:AP813" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C677:C724">
-    <cfRule type="cellIs" dxfId="120" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="16" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D560">
-    <cfRule type="cellIs" dxfId="119" priority="110" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="125" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="109" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="124" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="108" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="123" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D562:D563 D568:D569 D571:D575 D577 D579:D581 D583 D586 D588:D590 D607:D608 D613 D627:D628 D655:D656 D659 D663:D665 D667">
-    <cfRule type="cellIs" dxfId="116" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="99" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="98" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="97" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D596:D598 D604">
-    <cfRule type="cellIs" dxfId="113" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="85" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="86" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="87" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D617:D618 D623">
-    <cfRule type="cellIs" dxfId="110" priority="67" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="82" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="83" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="84" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D637:D638">
-    <cfRule type="cellIs" dxfId="107" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="81" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="79" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="80" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D647:D648">
-    <cfRule type="cellIs" dxfId="104" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="76" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="77" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="78" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D670:D682">
-    <cfRule type="cellIs" dxfId="101" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="25" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="26" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="27" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D684">
-    <cfRule type="cellIs" dxfId="98" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="31" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="33" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="32" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D686">
-    <cfRule type="cellIs" dxfId="95" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="36" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="34" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="35" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D691:D694">
-    <cfRule type="cellIs" dxfId="92" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="37" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="38" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="39" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D697">
-    <cfRule type="cellIs" dxfId="89" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="40" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="41" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="42" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D706:D707">
-    <cfRule type="cellIs" dxfId="86" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="22" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="23" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="24" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D714:D716">
-    <cfRule type="cellIs" dxfId="83" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="20" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="21" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="19" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D720:D724 D735:D802">
-    <cfRule type="cellIs" dxfId="80" priority="31" operator="equal">
+  <conditionalFormatting sqref="D720:D724 D735:D803">
+    <cfRule type="cellIs" dxfId="98" priority="46" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="47" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="48" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D726:D727">
-    <cfRule type="cellIs" dxfId="77" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="64" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="63" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="62" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D730:D731">
-    <cfRule type="cellIs" dxfId="74" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="58" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="57" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="56" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D733">
-    <cfRule type="cellIs" dxfId="71" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="53" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="54" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="55" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E197:E202 E214 E226:F226 E238:F238 E250:F250">
-    <cfRule type="cellIs" dxfId="68" priority="424" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="439" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="425" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="440" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E204:E205 E208 E216 E218:E219 E228:E231">
-    <cfRule type="cellIs" dxfId="66" priority="429" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="444" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="428" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="443" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401 E413 E425 E437:F437 E449:F449">
-    <cfRule type="cellIs" dxfId="64" priority="259" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="274" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="260" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="275" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E407:E410">
-    <cfRule type="cellIs" dxfId="62" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="206" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="192" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="207" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E415 E418">
-    <cfRule type="cellIs" dxfId="60" priority="263" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="278" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="264" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="279" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E427">
-    <cfRule type="cellIs" dxfId="58" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="229" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="213" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="228" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E430">
-    <cfRule type="cellIs" dxfId="56" priority="168" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="183" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="169" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="184" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:F263 F264">
-    <cfRule type="cellIs" dxfId="54" priority="411" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="426" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="412" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="427" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E269:F269 F270">
-    <cfRule type="cellIs" dxfId="52" priority="394" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="409" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="393" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="408" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E403:F403">
-    <cfRule type="cellIs" dxfId="50" priority="180" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="195" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="179" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="194" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E461:F463">
-    <cfRule type="cellIs" dxfId="48" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="227" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="226" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E468:F469">
-    <cfRule type="cellIs" dxfId="46" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="222" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="223" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F191 E192:F192">
-    <cfRule type="cellIs" dxfId="44" priority="507" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="522" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="506" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="521" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F193:F214">
-    <cfRule type="cellIs" dxfId="42" priority="436" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="451" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="437" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="452" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="cellIs" dxfId="40" priority="446" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="461" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="447" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="462" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260">
-    <cfRule type="cellIs" dxfId="38" priority="442" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="457" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="443" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="458" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F390 E391:F391 E396:E399">
-    <cfRule type="cellIs" dxfId="36" priority="318" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="333" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="319" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="334" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F392:F402">
-    <cfRule type="cellIs" dxfId="34" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="200" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="201" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F404:F414">
-    <cfRule type="cellIs" dxfId="32" priority="170" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="185" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="171" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="186" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:F426">
-    <cfRule type="cellIs" dxfId="30" priority="183" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="198" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="199" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F435">
-    <cfRule type="cellIs" dxfId="28" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="218" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="204" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="219" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F459">
-    <cfRule type="cellIs" dxfId="26" priority="275" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="290" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="276" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="291" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H191:H274">
-    <cfRule type="cellIs" dxfId="24" priority="341" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="356" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="342" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="357" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H390:H475">
-    <cfRule type="cellIs" dxfId="22" priority="232" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="247" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="233" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="248" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H550:H560">
-    <cfRule type="cellIs" dxfId="20" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="112" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="113" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J174:J190">
-    <cfRule type="expression" dxfId="18" priority="526">
+    <cfRule type="expression" dxfId="36" priority="541">
       <formula>D174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O212 O236 O260">
-    <cfRule type="cellIs" dxfId="17" priority="430" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="445" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="431" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="446" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O411 O435 O459">
-    <cfRule type="cellIs" dxfId="15" priority="265" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="280" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="266" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="281" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O174:P192 O390:P391">
-    <cfRule type="expression" dxfId="13" priority="523">
+    <cfRule type="expression" dxfId="31" priority="538">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q174:Q192 Q390:Q391">
-    <cfRule type="expression" dxfId="12" priority="525">
+    <cfRule type="expression" dxfId="30" priority="540">
       <formula>F174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R174:R196 R203:R208 R215:R220 R227:R232 R239:R244 R251:R256 R390:R395 R402:R407 R414:R419 R426:R431 R438:R443 R450:R455 R550:R553">
-    <cfRule type="expression" dxfId="11" priority="508">
+    <cfRule type="expression" dxfId="29" priority="523">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S174:S196 S203:S208 S216 S218:S219 S228:S231 S390:S395 S402:S407 S415 S417:S418 S427:S430">
-    <cfRule type="expression" dxfId="10" priority="522">
+    <cfRule type="expression" dxfId="28" priority="537">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T174:U195 X191:AC195 T390:U390 X390 Y390:AC394 U391 T393:U394 X393:X394 T402:U402 X402 Y402:Y403 U403 T405:U406 X405:Y406 Y414 Y426">
-    <cfRule type="expression" dxfId="9" priority="520">
+    <cfRule type="expression" dxfId="27" priority="535">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V174:W214 U263:V264 U269:V270 V390:W413 U462:V463 U468:V469">
-    <cfRule type="expression" dxfId="8" priority="456">
+    <cfRule type="expression" dxfId="26" priority="471">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X174:AC190">
-    <cfRule type="expression" dxfId="7" priority="518">
+    <cfRule type="expression" dxfId="25" priority="533">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD174:AD190">
-    <cfRule type="expression" dxfId="6" priority="532">
+    <cfRule type="expression" dxfId="24" priority="547">
       <formula>J174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD191:AD195">
-    <cfRule type="expression" dxfId="5" priority="528">
+    <cfRule type="expression" dxfId="23" priority="543">
       <formula>Q191="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD390:AD394">
-    <cfRule type="expression" dxfId="4" priority="327">
+    <cfRule type="expression" dxfId="22" priority="342">
       <formula>Q390="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE174:AF190">
-    <cfRule type="expression" dxfId="3" priority="530">
+    <cfRule type="expression" dxfId="21" priority="545">
       <formula>J174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE191:AF195">
-    <cfRule type="expression" dxfId="2" priority="535">
+    <cfRule type="expression" dxfId="20" priority="550">
       <formula>Q191="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE390:AF394">
-    <cfRule type="expression" dxfId="1" priority="328">
+    <cfRule type="expression" dxfId="19" priority="343">
       <formula>Q390="Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D808">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D804">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D805">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D806:D807">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D809:D813">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40685,7 +41287,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:Z110"/>
+  <dimension ref="A1:Z112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -47556,6 +48158,106 @@
       </c>
       <c r="Y110" t="s">
         <v>446</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>998</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C111" t="s">
+        <v>100</v>
+      </c>
+      <c r="D111">
+        <v>6</v>
+      </c>
+      <c r="E111" t="s">
+        <v>106</v>
+      </c>
+      <c r="G111" t="s">
+        <v>998</v>
+      </c>
+      <c r="H111">
+        <v>4</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>25</v>
+      </c>
+      <c r="K111">
+        <v>50</v>
+      </c>
+      <c r="L111">
+        <v>75</v>
+      </c>
+      <c r="M111">
+        <v>100</v>
+      </c>
+      <c r="P111" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>460</v>
+      </c>
+      <c r="R111" t="s">
+        <v>461</v>
+      </c>
+      <c r="S111" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>998</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C112" t="s">
+        <v>100</v>
+      </c>
+      <c r="D112">
+        <v>5</v>
+      </c>
+      <c r="E112" t="s">
+        <v>106</v>
+      </c>
+      <c r="G112" t="s">
+        <v>998</v>
+      </c>
+      <c r="H112">
+        <v>4</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>25</v>
+      </c>
+      <c r="K112">
+        <v>50</v>
+      </c>
+      <c r="L112">
+        <v>75</v>
+      </c>
+      <c r="M112">
+        <v>100</v>
+      </c>
+      <c r="P112" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>460</v>
+      </c>
+      <c r="R112" t="s">
+        <v>461</v>
+      </c>
+      <c r="S112" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -49935,7 +50637,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C28:C59">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50400,6 +51102,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100557C7523FAC84E43A0DA62C173857381" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4b9ddb1302998b61081aed2913076a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9bb5d252-d316-43f0-83d0-ec4a335d3ce7" xmlns:ns4="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3079d22dc9190cbddbf9f4c007b8016d" ns3:_="" ns4:_="">
     <xsd:import namespace="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
@@ -50622,12 +51330,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499CACD6-B6F0-4CF9-927E-84E37D5EF230}">
   <ds:schemaRefs>
@@ -50637,6 +51339,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFD8027B-57D9-4B92-B1B3-871595BA197C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19304C29-C31A-47A1-B855-8D09E823E92C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50653,21 +51372,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFD8027B-57D9-4B92-B1B3-871595BA197C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/inst/extdata/MetricScoring.xlsx
+++ b/inst/extdata/MetricScoring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BioMonTools_BenB/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="442" documentId="6_{E1038586-8D02-4FF7-859A-8FC7A176EA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34441B10-4786-4982-8DCD-0D968C2F4D4C}"/>
+  <xr:revisionPtr revIDLastSave="443" documentId="6_{E1038586-8D02-4FF7-859A-8FC7A176EA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69AED15F-33C7-4F64-A161-03FE77A594B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">index.scoring!$A$1:$Z$103</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$813</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metric.scoring!$A$1:$AP$802</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ScoringRegimes!$A$5:$C$17</definedName>
     <definedName name="FileName">NOTES!$B$8</definedName>
   </definedNames>
@@ -1671,7 +1671,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10065" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9976" uniqueCount="1046">
   <si>
     <t>Erik.Leppo@tetratech.com</t>
   </si>
@@ -4808,16 +4808,7 @@
     <t>WetWide_611489</t>
   </si>
   <si>
-    <t>100 * (18.43 - metric) / (18.43 - 0.23)</t>
-  </si>
-  <si>
-    <t>100 * (metric - 66.67) / (87.87 - 66.67)</t>
-  </si>
-  <si>
     <t>Narrow_52949</t>
-  </si>
-  <si>
-    <t>100 * (6.03 - metric) / (6.03 - 3.31)</t>
   </si>
 </sst>
 </file>
@@ -5153,187 +5144,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Title" xfId="1" builtinId="15"/>
   </cellStyles>
-  <dxfs count="140">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="125">
     <dxf>
       <fill>
         <patternFill>
@@ -5763,41 +5574,11 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5863,61 +5644,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5983,21 +5714,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6043,21 +5774,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6083,71 +5804,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6263,26 +5924,6 @@
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6298,16 +5939,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6383,6 +6014,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -6398,16 +6039,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6473,11 +6104,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6493,11 +6124,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6513,6 +6164,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color auto="1"/>
       </font>
       <fill>
@@ -6523,11 +6184,191 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6566,7 +6407,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Worksheet"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descriptions"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="139">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Link" dataDxfId="124">
       <calculatedColumnFormula>HYPERLINK(FileName&amp;A18&amp;"!A1",A18)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7716,7 +7557,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:AP813"/>
+  <dimension ref="A1:AP802"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -40388,892 +40229,496 @@
         <v>446</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A803" t="s">
-        <v>998</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C803" t="s">
-        <v>74</v>
-      </c>
-      <c r="D803" t="s">
-        <v>28</v>
-      </c>
-      <c r="E803">
-        <v>0.23</v>
-      </c>
-      <c r="F803" t="s">
-        <v>78</v>
-      </c>
-      <c r="G803">
-        <v>18.43</v>
-      </c>
-      <c r="H803" t="s">
-        <v>80</v>
-      </c>
-      <c r="J803" t="s">
-        <v>1045</v>
-      </c>
-      <c r="K803" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A804" t="s">
-        <v>998</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C804" t="s">
-        <v>85</v>
-      </c>
-      <c r="D804" t="s">
-        <v>28</v>
-      </c>
-      <c r="E804">
-        <v>0.91</v>
-      </c>
-      <c r="F804" t="s">
-        <v>78</v>
-      </c>
-      <c r="G804">
-        <v>30.01</v>
-      </c>
-      <c r="H804" t="s">
-        <v>80</v>
-      </c>
-      <c r="J804" t="s">
-        <v>1029</v>
-      </c>
-      <c r="K804" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A805" t="s">
-        <v>998</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C805" t="s">
-        <v>34</v>
-      </c>
-      <c r="D805" t="s">
-        <v>28</v>
-      </c>
-      <c r="E805">
-        <v>3.89</v>
-      </c>
-      <c r="F805" t="s">
-        <v>78</v>
-      </c>
-      <c r="G805" s="19" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H805" t="s">
-        <v>80</v>
-      </c>
-      <c r="J805" t="s">
-        <v>1030</v>
-      </c>
-      <c r="K805" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A806" t="s">
-        <v>998</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C806" t="s">
-        <v>133</v>
-      </c>
-      <c r="D806" t="s">
-        <v>14</v>
-      </c>
-      <c r="E806">
-        <v>3.56</v>
-      </c>
-      <c r="F806" t="s">
-        <v>78</v>
-      </c>
-      <c r="G806">
-        <v>31.95</v>
-      </c>
-      <c r="H806" t="s">
-        <v>80</v>
-      </c>
-      <c r="J806" t="s">
-        <v>1008</v>
-      </c>
-      <c r="K806" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A807" t="s">
-        <v>998</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C807" t="s">
-        <v>683</v>
-      </c>
-      <c r="D807" t="s">
-        <v>14</v>
-      </c>
-      <c r="E807">
-        <v>66.67</v>
-      </c>
-      <c r="F807" t="s">
-        <v>78</v>
-      </c>
-      <c r="G807">
-        <v>87.87</v>
-      </c>
-      <c r="H807" t="s">
-        <v>80</v>
-      </c>
-      <c r="J807" t="s">
-        <v>1046</v>
-      </c>
-      <c r="K807" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A808" t="s">
-        <v>998</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C808" t="s">
-        <v>87</v>
-      </c>
-      <c r="D808" t="s">
-        <v>14</v>
-      </c>
-      <c r="E808">
-        <v>3.02</v>
-      </c>
-      <c r="F808" t="s">
-        <v>78</v>
-      </c>
-      <c r="G808">
-        <v>35.81</v>
-      </c>
-      <c r="H808" t="s">
-        <v>80</v>
-      </c>
-      <c r="J808" t="s">
-        <v>1009</v>
-      </c>
-      <c r="K808" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A809" t="s">
-        <v>998</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C809" t="s">
-        <v>135</v>
-      </c>
-      <c r="D809" t="s">
-        <v>28</v>
-      </c>
-      <c r="E809">
-        <v>3.31</v>
-      </c>
-      <c r="F809" t="s">
-        <v>78</v>
-      </c>
-      <c r="G809">
-        <v>6.03</v>
-      </c>
-      <c r="H809" t="s">
-        <v>80</v>
-      </c>
-      <c r="J809" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K809" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A810" t="s">
-        <v>998</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C810" t="s">
-        <v>430</v>
-      </c>
-      <c r="D810" t="s">
-        <v>28</v>
-      </c>
-      <c r="E810">
-        <v>2</v>
-      </c>
-      <c r="F810" t="s">
-        <v>78</v>
-      </c>
-      <c r="G810">
-        <v>10.35</v>
-      </c>
-      <c r="H810" t="s">
-        <v>80</v>
-      </c>
-      <c r="J810" t="s">
-        <v>1001</v>
-      </c>
-      <c r="K810" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A811" t="s">
-        <v>998</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C811" t="s">
-        <v>239</v>
-      </c>
-      <c r="D811" t="s">
-        <v>28</v>
-      </c>
-      <c r="E811">
-        <v>0.86</v>
-      </c>
-      <c r="F811" t="s">
-        <v>78</v>
-      </c>
-      <c r="G811">
-        <v>52.68</v>
-      </c>
-      <c r="H811" t="s">
-        <v>80</v>
-      </c>
-      <c r="J811" t="s">
-        <v>1024</v>
-      </c>
-      <c r="K811" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A812" t="s">
-        <v>998</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C812" t="s">
-        <v>516</v>
-      </c>
-      <c r="D812" t="s">
-        <v>14</v>
-      </c>
-      <c r="E812">
-        <v>28.12</v>
-      </c>
-      <c r="F812" t="s">
-        <v>78</v>
-      </c>
-      <c r="G812">
-        <v>61.5</v>
-      </c>
-      <c r="H812" t="s">
-        <v>80</v>
-      </c>
-      <c r="J812" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K812" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A813" t="s">
-        <v>998</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C813" t="s">
-        <v>89</v>
-      </c>
-      <c r="D813" t="s">
-        <v>14</v>
-      </c>
-      <c r="E813">
-        <v>12.5</v>
-      </c>
-      <c r="F813" t="s">
-        <v>78</v>
-      </c>
-      <c r="G813">
-        <v>27.16</v>
-      </c>
-      <c r="H813" t="s">
-        <v>80</v>
-      </c>
-      <c r="J813" t="s">
-        <v>1003</v>
-      </c>
-      <c r="K813" t="s">
-        <v>446</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AP813" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
+  <autoFilter ref="A1:AP802" xr:uid="{93A70181-B22C-4671-9C22-4B8DA5FE66AB}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="C677:C724">
-    <cfRule type="cellIs" dxfId="138" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="16" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D560">
-    <cfRule type="cellIs" dxfId="137" priority="125" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="122" priority="123" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="124" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="123" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="120" priority="125" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D562:D563 D568:D569 D571:D575 D577 D579:D581 D583 D586 D588:D590 D607:D608 D613 D627:D628 D655:D656 D659 D663:D665 D667">
-    <cfRule type="cellIs" dxfId="134" priority="99" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="119" priority="97" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="98" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="97" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="117" priority="99" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D596:D598 D604">
-    <cfRule type="cellIs" dxfId="131" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="85" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="86" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="87" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D617:D618 D623">
-    <cfRule type="cellIs" dxfId="128" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="82" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="83" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="126" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="84" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D637:D638">
-    <cfRule type="cellIs" dxfId="125" priority="81" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="79" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="80" operator="equal">
       <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="81" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D647:D648">
-    <cfRule type="cellIs" dxfId="122" priority="76" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="76" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="77" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="78" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D670:D682">
-    <cfRule type="cellIs" dxfId="119" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="25" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="26" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="27" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D684">
-    <cfRule type="cellIs" dxfId="116" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="31" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="32" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="99" priority="33" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="32" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D686">
-    <cfRule type="cellIs" dxfId="113" priority="36" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="34" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="35" operator="equal">
       <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="96" priority="36" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D691:D694">
-    <cfRule type="cellIs" dxfId="110" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="37" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="38" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="39" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D697">
-    <cfRule type="cellIs" dxfId="107" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="40" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="41" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="42" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D706:D707">
-    <cfRule type="cellIs" dxfId="104" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="22" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="23" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="24" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D714:D716">
-    <cfRule type="cellIs" dxfId="101" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="19" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="20" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="21" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="19" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D720:D724">
+    <cfRule type="cellIs" dxfId="83" priority="46" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D720:D724 D735:D803">
-    <cfRule type="cellIs" dxfId="98" priority="46" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="47" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="48" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D726:D727">
-    <cfRule type="cellIs" dxfId="95" priority="64" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="80" priority="62" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="63" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="62" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="78" priority="64" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D730:D731">
-    <cfRule type="cellIs" dxfId="92" priority="58" operator="equal">
-      <formula>"Increase"</formula>
+    <cfRule type="cellIs" dxfId="77" priority="56" operator="equal">
+      <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="57" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="56" operator="equal">
-      <formula>"NA"</formula>
+    <cfRule type="cellIs" dxfId="75" priority="58" operator="equal">
+      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D733">
-    <cfRule type="cellIs" dxfId="89" priority="53" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="53" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="54" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="55" operator="equal">
+      <formula>"Increase"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D735:D802">
+    <cfRule type="cellIs" dxfId="71" priority="1" operator="equal">
+      <formula>"NA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="2" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E197:E202 E214 E226:F226 E238:F238 E250:F250">
-    <cfRule type="cellIs" dxfId="86" priority="439" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="439" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="440" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="440" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E204:E205 E208 E216 E218:E219 E228:E231">
-    <cfRule type="cellIs" dxfId="84" priority="444" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="443" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="444" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="443" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401 E413 E425 E437:F437 E449:F449">
-    <cfRule type="cellIs" dxfId="82" priority="274" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="274" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="275" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="275" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E407:E410">
-    <cfRule type="cellIs" dxfId="80" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="206" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="207" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="207" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E415 E418">
-    <cfRule type="cellIs" dxfId="78" priority="278" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="278" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="279" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="279" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E427">
-    <cfRule type="cellIs" dxfId="76" priority="229" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="228" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="57" priority="229" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="228" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E430">
-    <cfRule type="cellIs" dxfId="74" priority="183" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="183" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="184" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:F263 F264">
-    <cfRule type="cellIs" dxfId="72" priority="426" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="426" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="427" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="427" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E269:F269 F270">
-    <cfRule type="cellIs" dxfId="70" priority="409" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="408" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="409" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="408" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E403:F403">
-    <cfRule type="cellIs" dxfId="68" priority="195" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="194" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="195" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="194" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E461:F463">
-    <cfRule type="cellIs" dxfId="66" priority="227" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="226" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="47" priority="227" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="226" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E468:F469">
-    <cfRule type="cellIs" dxfId="64" priority="222" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="222" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="223" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="223" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F191 E192:F192">
-    <cfRule type="cellIs" dxfId="62" priority="522" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="521" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="522" operator="equal">
       <formula>"Increase"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="521" operator="equal">
-      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F193:F214">
-    <cfRule type="cellIs" dxfId="60" priority="451" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="451" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="452" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="452" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="cellIs" dxfId="58" priority="461" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="461" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="462" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="462" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F260">
-    <cfRule type="cellIs" dxfId="56" priority="457" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="457" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="458" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="458" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F390 E391:F391 E396:E399">
-    <cfRule type="cellIs" dxfId="54" priority="333" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="333" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="334" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="334" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F392:F402">
-    <cfRule type="cellIs" dxfId="52" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="200" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="201" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F404:F414">
-    <cfRule type="cellIs" dxfId="50" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="185" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="186" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="186" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F425:F426">
-    <cfRule type="cellIs" dxfId="48" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="198" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="199" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="199" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F435">
-    <cfRule type="cellIs" dxfId="46" priority="218" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="218" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="219" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="219" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F459">
-    <cfRule type="cellIs" dxfId="44" priority="290" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="290" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="291" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="291" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H191:H274">
-    <cfRule type="cellIs" dxfId="42" priority="356" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="356" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="357" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="357" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H390:H475">
-    <cfRule type="cellIs" dxfId="40" priority="247" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="247" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="248" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="248" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H550:H560">
-    <cfRule type="cellIs" dxfId="38" priority="112" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="112" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="113" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J174:J190">
-    <cfRule type="expression" dxfId="36" priority="541">
+    <cfRule type="expression" dxfId="18" priority="541">
       <formula>D174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O212 O236 O260">
-    <cfRule type="cellIs" dxfId="35" priority="445" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="445" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="446" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="446" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O411 O435 O459">
-    <cfRule type="cellIs" dxfId="33" priority="280" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="280" operator="equal">
       <formula>""</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="281" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="281" operator="equal">
       <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O174:P192 O390:P391">
-    <cfRule type="expression" dxfId="31" priority="538">
+    <cfRule type="expression" dxfId="13" priority="538">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q174:Q192 Q390:Q391">
-    <cfRule type="expression" dxfId="30" priority="540">
+    <cfRule type="expression" dxfId="12" priority="540">
       <formula>F174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R174:R196 R203:R208 R215:R220 R227:R232 R239:R244 R251:R256 R390:R395 R402:R407 R414:R419 R426:R431 R438:R443 R450:R455 R550:R553">
-    <cfRule type="expression" dxfId="29" priority="523">
+    <cfRule type="expression" dxfId="11" priority="523">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S174:S196 S203:S208 S216 S218:S219 S228:S231 S390:S395 S402:S407 S415 S417:S418 S427:S430">
-    <cfRule type="expression" dxfId="28" priority="537">
+    <cfRule type="expression" dxfId="10" priority="537">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T174:U195 X191:AC195 T390:U390 X390 Y390:AC394 U391 T393:U394 X393:X394 T402:U402 X402 Y402:Y403 U403 T405:U406 X405:Y406 Y414 Y426">
-    <cfRule type="expression" dxfId="27" priority="535">
+    <cfRule type="expression" dxfId="9" priority="535">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V174:W214 U263:V264 U269:V270 V390:W413 U462:V463 U468:V469">
-    <cfRule type="expression" dxfId="26" priority="471">
+    <cfRule type="expression" dxfId="8" priority="471">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X174:AC190">
-    <cfRule type="expression" dxfId="25" priority="533">
+    <cfRule type="expression" dxfId="7" priority="533">
       <formula>E174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD174:AD190">
-    <cfRule type="expression" dxfId="24" priority="547">
+    <cfRule type="expression" dxfId="6" priority="547">
       <formula>J174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD191:AD195">
-    <cfRule type="expression" dxfId="23" priority="543">
+    <cfRule type="expression" dxfId="5" priority="543">
       <formula>Q191="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD390:AD394">
-    <cfRule type="expression" dxfId="22" priority="342">
+    <cfRule type="expression" dxfId="4" priority="342">
       <formula>Q390="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE174:AF190">
-    <cfRule type="expression" dxfId="21" priority="545">
+    <cfRule type="expression" dxfId="3" priority="545">
       <formula>J174="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE191:AF195">
-    <cfRule type="expression" dxfId="20" priority="550">
+    <cfRule type="expression" dxfId="2" priority="550">
       <formula>Q191="Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE390:AF394">
-    <cfRule type="expression" dxfId="19" priority="343">
+    <cfRule type="expression" dxfId="1" priority="343">
       <formula>Q390="Increase"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D808">
-    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D804">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D805">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D806:D807">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"Increase"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D809:D813">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"NA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"Increase"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -48215,7 +47660,7 @@
         <v>998</v>
       </c>
       <c r="B112" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C112" t="s">
         <v>100</v>
@@ -48310,15 +47755,15 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="str" cm="1">
-        <f t="array" ref="A4:A29">_xlfn.UNIQUE(metric.scoring!A2:A999)</f>
+        <f t="array" ref="A4:A29">_xlfn.UNIQUE(metric.scoring!A2:A988)</f>
         <v>MBSS_2005_Bugs</v>
       </c>
       <c r="B4" cm="1">
-        <f t="array" ref="B4">MAX(IF(metric.scoring!$A$2:$A$999=$A4,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B4">MAX(IF(metric.scoring!$A$2:$A$988=$A4,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>3</v>
       </c>
       <c r="C4" cm="1">
-        <f t="array" ref="C4">MAX(IF(metric.scoring!$A$2:$A$999=$A4,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C4">MAX(IF(metric.scoring!$A$2:$A$988=$A4,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>2</v>
       </c>
       <c r="D4">
@@ -48331,11 +47776,11 @@
         <v>MBSS_2005_Fish</v>
       </c>
       <c r="B5" cm="1">
-        <f t="array" ref="B5">MAX(IF(metric.scoring!$A$2:$A$999=$A5,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B5">MAX(IF(metric.scoring!$A$2:$A$988=$A5,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>11</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5">MAX(IF(metric.scoring!$A$2:$A$999=$A5,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C5">MAX(IF(metric.scoring!$A$2:$A$988=$A5,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>10</v>
       </c>
       <c r="D5">
@@ -48348,11 +47793,11 @@
         <v>MSW_1999_Bugs</v>
       </c>
       <c r="B6" cm="1">
-        <f t="array" ref="B6">MAX(IF(metric.scoring!$A$2:$A$999=$A6,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B6">MAX(IF(metric.scoring!$A$2:$A$988=$A6,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>3</v>
       </c>
       <c r="C6" cm="1">
-        <f t="array" ref="C6">MAX(IF(metric.scoring!$A$2:$A$999=$A6,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C6">MAX(IF(metric.scoring!$A$2:$A$988=$A6,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D6">
@@ -48365,11 +47810,11 @@
         <v>WSA_2006_Bugs</v>
       </c>
       <c r="B7" cm="1">
-        <f t="array" ref="B7">MAX(IF(metric.scoring!$A$2:$A$999=$A7,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B7">MAX(IF(metric.scoring!$A$2:$A$988=$A7,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C7" cm="1">
-        <f t="array" ref="C7">MAX(IF(metric.scoring!$A$2:$A$999=$A7,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C7">MAX(IF(metric.scoring!$A$2:$A$988=$A7,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D7">
@@ -48382,11 +47827,11 @@
         <v>BCG_PacNW_L1</v>
       </c>
       <c r="B8" cm="1">
-        <f t="array" ref="B8">MAX(IF(metric.scoring!$A$2:$A$999=$A8,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B8">MAX(IF(metric.scoring!$A$2:$A$988=$A8,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C8" cm="1">
-        <f t="array" ref="C8">MAX(IF(metric.scoring!$A$2:$A$999=$A8,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C8">MAX(IF(metric.scoring!$A$2:$A$988=$A8,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D8">
@@ -48399,11 +47844,11 @@
         <v>MBISQ_2015</v>
       </c>
       <c r="B9" cm="1">
-        <f t="array" ref="B9">MAX(IF(metric.scoring!$A$2:$A$999=$A9,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B9">MAX(IF(metric.scoring!$A$2:$A$988=$A9,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C9" cm="1">
-        <f t="array" ref="C9">MAX(IF(metric.scoring!$A$2:$A$999=$A9,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C9">MAX(IF(metric.scoring!$A$2:$A$988=$A9,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D9">
@@ -48416,11 +47861,11 @@
         <v>GADNR_2009</v>
       </c>
       <c r="B10" cm="1">
-        <f t="array" ref="B10">MAX(IF(metric.scoring!$A$2:$A$999=$A10,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B10">MAX(IF(metric.scoring!$A$2:$A$988=$A10,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C10" cm="1">
-        <f t="array" ref="C10">MAX(IF(metric.scoring!$A$2:$A$999=$A10,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C10">MAX(IF(metric.scoring!$A$2:$A$988=$A10,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>5</v>
       </c>
       <c r="D10">
@@ -48433,11 +47878,11 @@
         <v>GBI_MS_2013</v>
       </c>
       <c r="B11" cm="1">
-        <f t="array" ref="B11">MAX(IF(metric.scoring!$A$2:$A$999=$A11,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B11">MAX(IF(metric.scoring!$A$2:$A$988=$A11,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C11" cm="1">
-        <f t="array" ref="C11">MAX(IF(metric.scoring!$A$2:$A$999=$A11,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C11">MAX(IF(metric.scoring!$A$2:$A$988=$A11,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D11">
@@ -48450,11 +47895,11 @@
         <v>GADNR_Fish_2005</v>
       </c>
       <c r="B12" cm="1">
-        <f t="array" ref="B12">MAX(IF(metric.scoring!$A$2:$A$999=$A12,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B12">MAX(IF(metric.scoring!$A$2:$A$988=$A12,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C12" cm="1">
-        <f t="array" ref="C12">MAX(IF(metric.scoring!$A$2:$A$999=$A12,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C12">MAX(IF(metric.scoring!$A$2:$A$988=$A12,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D12">
@@ -48467,11 +47912,11 @@
         <v>PADEP_Freestone</v>
       </c>
       <c r="B13" cm="1">
-        <f t="array" ref="B13">MAX(IF(metric.scoring!$A$2:$A$999=$A13,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B13">MAX(IF(metric.scoring!$A$2:$A$988=$A13,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C13" cm="1">
-        <f t="array" ref="C13">MAX(IF(metric.scoring!$A$2:$A$999=$A13,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C13">MAX(IF(metric.scoring!$A$2:$A$988=$A13,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D13">
@@ -48484,11 +47929,11 @@
         <v>WV_GLIMPSS</v>
       </c>
       <c r="B14" cm="1">
-        <f t="array" ref="B14">MAX(IF(metric.scoring!$A$2:$A$999=$A14,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B14">MAX(IF(metric.scoring!$A$2:$A$988=$A14,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>4</v>
       </c>
       <c r="C14" cm="1">
-        <f t="array" ref="C14">MAX(IF(metric.scoring!$A$2:$A$999=$A14,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C14">MAX(IF(metric.scoring!$A$2:$A$988=$A14,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D14">
@@ -48501,11 +47946,11 @@
         <v>MIEGLE_2020</v>
       </c>
       <c r="B15" cm="1">
-        <f t="array" ref="B15">MAX(IF(metric.scoring!$A$2:$A$999=$A15,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B15">MAX(IF(metric.scoring!$A$2:$A$988=$A15,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>5</v>
       </c>
       <c r="C15" cm="1">
-        <f t="array" ref="C15">MAX(IF(metric.scoring!$A$2:$A$999=$A15,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C15">MAX(IF(metric.scoring!$A$2:$A$988=$A15,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>5</v>
       </c>
       <c r="D15">
@@ -48518,11 +47963,11 @@
         <v>GADNR_Fish_2020</v>
       </c>
       <c r="B16" cm="1">
-        <f t="array" ref="B16">MAX(IF(metric.scoring!$A$2:$A$999=$A16,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B16">MAX(IF(metric.scoring!$A$2:$A$988=$A16,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>5</v>
       </c>
       <c r="C16" cm="1">
-        <f t="array" ref="C16">MAX(IF(metric.scoring!$A$2:$A$999=$A16,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C16">MAX(IF(metric.scoring!$A$2:$A$988=$A16,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>5</v>
       </c>
       <c r="D16">
@@ -48535,11 +47980,11 @@
         <v>MassDEP_2020_Bugs</v>
       </c>
       <c r="B17" cm="1">
-        <f t="array" ref="B17">MAX(IF(metric.scoring!$A$2:$A$999=$A17,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B17">MAX(IF(metric.scoring!$A$2:$A$988=$A17,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>3</v>
       </c>
       <c r="C17" cm="1">
-        <f t="array" ref="C17">MAX(IF(metric.scoring!$A$2:$A$999=$A17,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C17">MAX(IF(metric.scoring!$A$2:$A$988=$A17,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D17">
@@ -48552,11 +47997,11 @@
         <v>SNEP_2020_Bugs</v>
       </c>
       <c r="B18" cm="1">
-        <f t="array" ref="B18">MAX(IF(metric.scoring!$A$2:$A$999=$A18,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B18">MAX(IF(metric.scoring!$A$2:$A$988=$A18,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>1</v>
       </c>
       <c r="C18" cm="1">
-        <f t="array" ref="C18">MAX(IF(metric.scoring!$A$2:$A$999=$A18,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C18">MAX(IF(metric.scoring!$A$2:$A$988=$A18,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>2</v>
       </c>
       <c r="D18">
@@ -48569,11 +48014,11 @@
         <v>FFXCOVA_2018</v>
       </c>
       <c r="B19" cm="1">
-        <f t="array" ref="B19">MAX(IF(metric.scoring!$A$2:$A$999=$A19,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B19">MAX(IF(metric.scoring!$A$2:$A$988=$A19,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>7</v>
       </c>
       <c r="C19" cm="1">
-        <f t="array" ref="C19">MAX(IF(metric.scoring!$A$2:$A$999=$A19,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C19">MAX(IF(metric.scoring!$A$2:$A$988=$A19,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>7</v>
       </c>
       <c r="D19">
@@ -48586,11 +48031,11 @@
         <v>IEPA_2021_Bugs</v>
       </c>
       <c r="B20" cm="1">
-        <f t="array" ref="B20">MAX(IF(metric.scoring!$A$2:$A$999=$A20,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B20">MAX(IF(metric.scoring!$A$2:$A$988=$A20,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>3</v>
       </c>
       <c r="C20" cm="1">
-        <f t="array" ref="C20">MAX(IF(metric.scoring!$A$2:$A$999=$A20,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C20">MAX(IF(metric.scoring!$A$2:$A$988=$A20,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D20">
@@ -48603,11 +48048,11 @@
         <v>NJ_NorthernFish_2005</v>
       </c>
       <c r="B21" cm="1">
-        <f t="array" ref="B21">MAX(IF(metric.scoring!$A$2:$A$999=$A21,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B21">MAX(IF(metric.scoring!$A$2:$A$988=$A21,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>2</v>
       </c>
       <c r="C21" cm="1">
-        <f t="array" ref="C21">MAX(IF(metric.scoring!$A$2:$A$999=$A21,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C21">MAX(IF(metric.scoring!$A$2:$A$988=$A21,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>3</v>
       </c>
       <c r="D21">
@@ -48620,11 +48065,11 @@
         <v>IDEM_2021_Diatoms</v>
       </c>
       <c r="B22" cm="1">
-        <f t="array" ref="B22">MAX(IF(metric.scoring!$A$2:$A$999=$A22,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B22">MAX(IF(metric.scoring!$A$2:$A$988=$A22,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>3</v>
       </c>
       <c r="C22" cm="1">
-        <f t="array" ref="C22">MAX(IF(metric.scoring!$A$2:$A$999=$A22,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C22">MAX(IF(metric.scoring!$A$2:$A$988=$A22,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D22">
@@ -48637,11 +48082,11 @@
         <v>SCMB_IBI</v>
       </c>
       <c r="B23" cm="1">
-        <f t="array" ref="B23">MAX(IF(metric.scoring!$A$2:$A$999=$A23,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B23">MAX(IF(metric.scoring!$A$2:$A$988=$A23,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>2</v>
       </c>
       <c r="C23" cm="1">
-        <f t="array" ref="C23">MAX(IF(metric.scoring!$A$2:$A$999=$A23,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C23">MAX(IF(metric.scoring!$A$2:$A$988=$A23,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>4</v>
       </c>
       <c r="D23">
@@ -48654,11 +48099,11 @@
         <v>CO_Bugs_2006</v>
       </c>
       <c r="B24" cm="1">
-        <f t="array" ref="B24">MAX(IF(metric.scoring!$A$2:$A$999=$A24,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B24">MAX(IF(metric.scoring!$A$2:$A$988=$A24,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>5</v>
       </c>
       <c r="C24" cm="1">
-        <f t="array" ref="C24">MAX(IF(metric.scoring!$A$2:$A$999=$A24,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C24">MAX(IF(metric.scoring!$A$2:$A$988=$A24,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>5</v>
       </c>
       <c r="D24">
@@ -48671,11 +48116,11 @@
         <v>MN_IBI_Bugs</v>
       </c>
       <c r="B25" cm="1">
-        <f t="array" ref="B25">MAX(IF(metric.scoring!$A$2:$A$999=$A25,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B25">MAX(IF(metric.scoring!$A$2:$A$988=$A25,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>9</v>
       </c>
       <c r="C25" cm="1">
-        <f t="array" ref="C25">MAX(IF(metric.scoring!$A$2:$A$999=$A25,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C25">MAX(IF(metric.scoring!$A$2:$A$988=$A25,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>9</v>
       </c>
       <c r="D25">
@@ -48688,11 +48133,11 @@
         <v>WY_WSII_2023</v>
       </c>
       <c r="B26" cm="1">
-        <f t="array" ref="B26">MAX(IF(metric.scoring!$A$2:$A$999=$A26,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B26">MAX(IF(metric.scoring!$A$2:$A$988=$A26,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>12</v>
       </c>
       <c r="C26" cm="1">
-        <f t="array" ref="C26">MAX(IF(metric.scoring!$A$2:$A$999=$A26,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C26">MAX(IF(metric.scoring!$A$2:$A$988=$A26,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>13</v>
       </c>
       <c r="D26">
@@ -48705,11 +48150,11 @@
         <v>MN_IBI_Fish</v>
       </c>
       <c r="B27" cm="1">
-        <f t="array" ref="B27">MAX(IF(metric.scoring!$A$2:$A$999=$A27,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B27">MAX(IF(metric.scoring!$A$2:$A$988=$A27,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>9</v>
       </c>
       <c r="C27" cm="1">
-        <f t="array" ref="C27">MAX(IF(metric.scoring!$A$2:$A$999=$A27,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C27">MAX(IF(metric.scoring!$A$2:$A$988=$A27,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>8</v>
       </c>
       <c r="D27">
@@ -48722,11 +48167,11 @@
         <v>EGLE_2025</v>
       </c>
       <c r="B28" cm="1">
-        <f t="array" ref="B28">MAX(IF(metric.scoring!$A$2:$A$999=$A28,LEN(metric.scoring!$E$2:$E$999)))</f>
+        <f t="array" ref="B28">MAX(IF(metric.scoring!$A$2:$A$988=$A28,LEN(metric.scoring!$E$2:$E$988)))</f>
         <v>5</v>
       </c>
       <c r="C28" cm="1">
-        <f t="array" ref="C28">MAX(IF(metric.scoring!$A$2:$A$999=$A28,LEN(metric.scoring!$G$2:$G$999)))</f>
+        <f t="array" ref="C28">MAX(IF(metric.scoring!$A$2:$A$988=$A28,LEN(metric.scoring!$G$2:$G$988)))</f>
         <v>5</v>
       </c>
       <c r="D28">
@@ -50637,7 +50082,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C28:C59">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"NA"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -51093,21 +50538,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100557C7523FAC84E43A0DA62C173857381" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4b9ddb1302998b61081aed2913076a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9bb5d252-d316-43f0-83d0-ec4a335d3ce7" xmlns:ns4="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3079d22dc9190cbddbf9f4c007b8016d" ns3:_="" ns4:_="">
     <xsd:import namespace="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
@@ -51330,10 +50760,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499CACD6-B6F0-4CF9-927E-84E37D5EF230}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19304C29-C31A-47A1-B855-8D09E823E92C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
+    <ds:schemaRef ds:uri="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -51356,20 +50812,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19304C29-C31A-47A1-B855-8D09E823E92C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{499CACD6-B6F0-4CF9-927E-84E37D5EF230}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9bb5d252-d316-43f0-83d0-ec4a335d3ce7"/>
-    <ds:schemaRef ds:uri="c0f75fa0-0a50-44a1-84b6-f6a4c66e6868"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>